--- a/site/docs/cert-prep/method.xlsx
+++ b/site/docs/cert-prep/method.xlsx
@@ -61,8 +61,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -201,22 +201,22 @@
     <row r="7">
       <c r="A7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">CHAMP</t>
+          <t xml:space="preserve">CSAM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retire hardware with data-wipe evidence</t>
+          <t xml:space="preserve">Respond to a publisher audit letter with prepared evidence</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">devices.csv</t>
+          <t xml:space="preserve">audit-letter.md, proofs-of-purchase.csv, audit-installs.csv</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">07</t>
+          <t xml:space="preserve">08</t>
         </is>
       </c>
     </row>
@@ -228,7 +228,7 @@
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Track refresh against budget</t>
+          <t xml:space="preserve">Retire hardware with data-wipe evidence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="0">
@@ -245,22 +245,22 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AIGP</t>
+          <t xml:space="preserve">CHAMP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Tier a new AI use case</t>
+          <t xml:space="preserve">Track refresh against budget</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ai-systems.csv</t>
+          <t xml:space="preserve">devices.csv</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">06</t>
+          <t xml:space="preserve">07</t>
         </is>
       </c>
     </row>
@@ -272,7 +272,7 @@
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Log data provenance and check prohibited practices</t>
+          <t xml:space="preserve">Tier a new AI use case</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="0">
@@ -289,22 +289,22 @@
     <row r="11">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ITIL 4 Foundation</t>
+          <t xml:space="preserve">AIGP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Feed the inventory into configuration management</t>
+          <t xml:space="preserve">Log data provenance and check prohibited practices</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">apps.csv</t>
+          <t xml:space="preserve">ai-systems.csv</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">02</t>
+          <t xml:space="preserve">06</t>
         </is>
       </c>
     </row>
@@ -316,34 +316,34 @@
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Manage suppliers and renewals</t>
+          <t xml:space="preserve">Feed the inventory into configuration management</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">licenses.csv</t>
+          <t xml:space="preserve">apps.csv</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">04</t>
+          <t xml:space="preserve">02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IAM Certificate</t>
+          <t xml:space="preserve">ITIL 4 Foundation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Treat the portfolio as a managed asset base</t>
+          <t xml:space="preserve">Manage suppliers and renewals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">apps.csv</t>
+          <t xml:space="preserve">licenses.csv</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="0">
@@ -360,15 +360,37 @@
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">Treat the portfolio as a managed asset base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">apps.csv</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">IAM Certificate</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">Set a policy with real scope</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr" s="0">
+      <c r="C15" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">council-draft.md</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr" s="0">
+      <c r="D15" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">01</t>
         </is>
